--- a/plantillas/12.xlsx
+++ b/plantillas/12.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cargue" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Listas" sheetId="2" state="hidden" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Productos" sheetId="3" state="hidden" r:id="rId3"/>
+    <sheet name="Cargue" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Listas" sheetId="2" state="hidden" r:id="rId2"/>
+    <sheet name="Productos" sheetId="3" state="hidden" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="MARCA_1">Listas!$D$2:$D$2</definedName>
@@ -8941,7 +8941,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -8961,7 +8961,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -9041,7 +9041,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -9241,7 +9241,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -9401,7 +9401,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -10219,7 +10219,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>24.10.2026</t>
+          <t>28.10.2026</t>
         </is>
       </c>
     </row>

--- a/plantillas/12.xlsx
+++ b/plantillas/12.xlsx
@@ -9261,7 +9261,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -10219,7 +10219,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>28.10.2026</t>
+          <t>29.10.2026</t>
         </is>
       </c>
     </row>

--- a/plantillas/12.xlsx
+++ b/plantillas/12.xlsx
@@ -9341,7 +9341,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -9401,7 +9401,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -10219,7 +10219,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>29.10.2026</t>
+          <t>30.10.2026</t>
         </is>
       </c>
     </row>
